--- a/AAII_Financials/Quarterly/KKPNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KKPNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="92">
   <si>
     <t>KKPNY</t>
   </si>
@@ -656,172 +656,180 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45107</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45199</v>
       </c>
       <c r="M7" s="2">
         <v>45107</v>
       </c>
       <c r="N7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="O7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -858,86 +866,92 @@
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3">
         <v>1513000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1452500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1428700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1422400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1486300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1426900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1363800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1325000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1367400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1348200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1410500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1500600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1656600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1914700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3201000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1629200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>3353500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>1548400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>3078800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>1539400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>3213400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>1584200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>3229100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>1934400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>4039100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>2016600</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -974,86 +988,92 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>388800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>382600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>366700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>352600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>388100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>344600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>323700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>320500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>354100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>329000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>324000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>355700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>422600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>401800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>718800</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>809100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>365500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>711500</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="3">
         <v>766300</v>
       </c>
-      <c r="AJ9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="3">
         <v>765200</v>
       </c>
-      <c r="AL9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="3">
         <v>1247800</v>
       </c>
-      <c r="AN9" s="3" t="s">
+      <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,86 +1110,92 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1124200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1069900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1062000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1069800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1098200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1082300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1040000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1004500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1013400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1019200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1086500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1144900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1234000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1512900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>2482200</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>2544400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>1182900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>2367300</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="3">
         <v>2447100</v>
       </c>
-      <c r="AJ10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="3">
         <v>2463900</v>
       </c>
-      <c r="AL10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="3">
         <v>2791300</v>
       </c>
-      <c r="AN10" s="3" t="s">
+      <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1210,8 +1236,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1326,8 +1354,14 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1442,8 +1476,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1480,86 +1520,92 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-10000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-3300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-4300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-6500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>2200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-896100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>8200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-8000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>10400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>11300</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-232700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>92900</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3">
         <v>15400</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" s="3">
         <v>45000</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK14" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM14" s="3">
         <v>10100</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN14" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1602,80 +1648,86 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="3">
         <v>351500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>371100</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W15" s="3">
         <v>386200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>371600</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA15" s="3">
         <v>429800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>438100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>39700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>41600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>885800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>41900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>897800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>41000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>829000</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK15" s="3">
         <v>795500</v>
       </c>
-      <c r="AJ15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="3">
         <v>779800</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO15" s="3">
         <v>883900</v>
       </c>
-      <c r="AN15" s="3" t="s">
+      <c r="AP15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1713,8 +1765,10 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1757,80 +1811,86 @@
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>1094600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1106700</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>207400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1085100</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>1156400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1256700</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>2718700</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>2895700</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI17" s="3">
         <v>2603400</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="3">
         <v>2787000</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="3">
         <v>2808300</v>
       </c>
-      <c r="AL17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO17" s="3">
         <v>3407600</v>
       </c>
-      <c r="AN17" s="3" t="s">
+      <c r="AP17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1873,80 +1933,86 @@
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>334000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>315700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>1156400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>239900</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>254200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>243900</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>482300</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>457800</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>475400</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="3">
         <v>426400</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="3">
         <v>420700</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO18" s="3">
         <v>631500</v>
       </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AP18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1987,8 +2053,10 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2031,80 +2099,86 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>-64200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-59700</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>-55000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-50000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-62200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-67700</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-137600</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-198700</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-114200</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-190700</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-85300</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO20" s="3">
         <v>-405000</v>
       </c>
-      <c r="AN20" s="3" t="s">
+      <c r="AP20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2147,80 +2221,86 @@
       <c r="P21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>632200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>627100</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>1487500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>561400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>621800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>614200</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>1241100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>1172300</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>1196800</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="3">
         <v>1032200</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM21" s="3">
         <v>1125400</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="3">
         <v>1110400</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AP21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2257,71 +2337,71 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>5500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>5400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>5400</v>
-      </c>
-      <c r="R22" s="3">
-        <v>4300</v>
       </c>
       <c r="S22" s="3">
         <v>5400</v>
       </c>
       <c r="T22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="U22" s="3">
         <v>5400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="W22" s="3">
         <v>6300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>5100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>5000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>6200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>5500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>6800</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>8600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>17600</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>18900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>8900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>18700</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>0</v>
+      <c r="AJ22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
@@ -2335,8 +2415,14 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2379,80 +2465,86 @@
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>264400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>251700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>1095000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>184800</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>186500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>169400</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>327000</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>240100</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI23" s="3">
         <v>342600</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="3">
         <v>235600</v>
       </c>
-      <c r="AJ23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM23" s="3">
         <v>335500</v>
       </c>
-      <c r="AL23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO23" s="3">
         <v>226500</v>
       </c>
-      <c r="AN23" s="3" t="s">
+      <c r="AP23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2495,80 +2587,86 @@
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>62000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>57500</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>248600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>40800</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>39300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>33900</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>71800</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>184500</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI24" s="3">
         <v>74700</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK24" s="3">
         <v>61700</v>
       </c>
-      <c r="AJ24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM24" s="3">
         <v>71800</v>
       </c>
-      <c r="AL24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO24" s="3">
         <v>38700</v>
       </c>
-      <c r="AN24" s="3" t="s">
+      <c r="AP24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2683,8 +2781,14 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2721,86 +2825,92 @@
       <c r="N26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>211600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>228000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>202400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>194200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>170200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>199200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>846400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>143900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>174500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>137000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>147300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>135500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>98100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>384600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>255300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>106500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>55600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>104100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>267900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>107600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>173900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>111100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>263700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>108000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>187800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2837,86 +2947,92 @@
       <c r="N27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>211600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>228000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>202400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>194200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>170200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>199200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>846400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>143900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>174500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>137000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>147300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>135500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>98100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>384600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>255300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>106500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>104100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>267900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>107600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>116700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>111100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>263700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>108000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>127900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3031,8 +3147,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3075,80 +3197,86 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-1100</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>1100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC29" s="3">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>15300</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>8300</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-18700</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM29" s="3">
         <v>5600</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO29" s="3">
         <v>79800</v>
       </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3263,8 +3391,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3379,8 +3513,14 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3423,80 +3563,86 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>64200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>59700</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>55000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>50000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>62200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>67700</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>137600</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>198700</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" s="3">
         <v>114200</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK32" s="3">
         <v>190700</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM32" s="3">
         <v>85300</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO32" s="3">
         <v>405000</v>
       </c>
-      <c r="AN32" s="3" t="s">
+      <c r="AP32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3533,86 +3679,92 @@
       <c r="N33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>211600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>228000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>202400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>193100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>170200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>199200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>846400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>143900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>174500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>137000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>148400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>135500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>98100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>384600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>270600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>106500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>104100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>249200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>107600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>111100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>111100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>269300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>108000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>207800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3727,8 +3879,14 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3765,207 +3923,219 @@
       <c r="N35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>211600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>228000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>202400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>193100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>170200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>199200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>846400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>143900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>174500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>137000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>148400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>135500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>98100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>384600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>270600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>106500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>104100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>249200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>107600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>111100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>111100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>269300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>108000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>207800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45107</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45199</v>
       </c>
       <c r="M38" s="2">
         <v>45107</v>
       </c>
       <c r="N38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="O38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4006,8 +4176,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4048,153 +4220,161 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>327900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>517700</v>
+      </c>
+      <c r="F41" s="3">
         <v>475500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>368800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1340300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>685400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>900000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1152200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>673200</v>
-      </c>
-      <c r="K41" s="3">
-        <v>258700</v>
-      </c>
-      <c r="L41" s="3">
-        <v>431800</v>
       </c>
       <c r="M41" s="3">
         <v>258700</v>
       </c>
       <c r="N41" s="3">
+        <v>431800</v>
+      </c>
+      <c r="O41" s="3">
+        <v>258700</v>
+      </c>
+      <c r="P41" s="3">
         <v>477000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>441900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>461500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>476600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>731300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>859700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3">
         <v>577700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="3">
         <v>595400</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>989500</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>894200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>448200</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>702600</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI41" s="3">
         <v>1127600</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK41" s="3">
         <v>960400</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM41" s="3">
         <v>1027700</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO41" s="3">
         <v>1383900</v>
       </c>
-      <c r="AN41" s="3" t="s">
+      <c r="AP41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>150800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>213700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>70500</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>144900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>331100</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>242100</v>
-      </c>
-      <c r="K42" s="3">
-        <v>177900</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
       </c>
       <c r="M42" s="3">
         <v>177900</v>
@@ -4203,114 +4383,120 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>177900</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>141800</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S42" s="3">
         <v>251400</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U42" s="3">
         <v>340400</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W42" s="3">
         <v>269800</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="3">
         <v>269300</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3">
         <v>321000</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="3">
         <v>2400</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>590300</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI42" s="3">
         <v>1143000</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK42" s="3">
         <v>1570800</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM42" s="3">
         <v>268200</v>
       </c>
-      <c r="AL42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO42" s="3">
         <v>164300</v>
       </c>
-      <c r="AN42" s="3" t="s">
+      <c r="AP42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>923100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
         <v>716200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>856100</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3">
         <v>582900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>749000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
         <v>646600</v>
-      </c>
-      <c r="K43" s="3">
-        <v>774000</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>774000</v>
@@ -4319,114 +4505,120 @@
         <v>5</v>
       </c>
       <c r="O43" s="3">
+        <v>774000</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="3">
         <v>877200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="3">
         <v>864000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3">
         <v>784900</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3">
         <v>786100</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3">
         <v>684200</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
         <v>878200</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>925800</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>997600</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>1048000</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI43" s="3">
         <v>1022200</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK43" s="3">
         <v>1148900</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM43" s="3">
         <v>877400</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO43" s="3">
         <v>899100</v>
       </c>
-      <c r="AN43" s="3" t="s">
+      <c r="AP43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3">
         <v>48100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>50500</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3">
         <v>46600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>45000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>47500</v>
-      </c>
-      <c r="K44" s="3">
-        <v>62200</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>62200</v>
@@ -4435,172 +4627,178 @@
         <v>5</v>
       </c>
       <c r="O44" s="3">
+        <v>62200</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3">
         <v>54300</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3">
         <v>57700</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3">
         <v>40100</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3">
         <v>43400</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3">
         <v>46900</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>53500</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>63000</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>72900</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>68600</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI44" s="3">
         <v>63700</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK44" s="3">
         <v>60600</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM44" s="3">
         <v>66200</v>
       </c>
-      <c r="AL44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO44" s="3">
         <v>55200</v>
       </c>
-      <c r="AN44" s="3" t="s">
+      <c r="AP44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1335200</v>
+      </c>
+      <c r="F45" s="3">
         <v>35200</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>1080800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>33100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1122000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>21000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1052100</v>
       </c>
       <c r="M45" s="3">
         <v>2200</v>
       </c>
       <c r="N45" s="3">
+        <v>1052100</v>
+      </c>
+      <c r="O45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P45" s="3">
         <v>1084300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>26600</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S45" s="3">
         <v>117500</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3">
         <v>21200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3">
         <v>11000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>4400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>24500</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4610,15 +4808,15 @@
       <c r="AH45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK45" s="3">
         <v>1200500</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK45" s="3">
-        <v>0</v>
-      </c>
       <c r="AL45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4628,153 +4826,165 @@
       <c r="AN45" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1464600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1852900</v>
+      </c>
+      <c r="F46" s="3">
         <v>1585100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1345900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2421100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1574700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2030400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2274200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1703300</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1275100</v>
-      </c>
-      <c r="L46" s="3">
-        <v>1483900</v>
       </c>
       <c r="M46" s="3">
         <v>1275100</v>
       </c>
       <c r="N46" s="3">
+        <v>1483900</v>
+      </c>
+      <c r="O46" s="3">
+        <v>1275100</v>
+      </c>
+      <c r="P46" s="3">
         <v>1561300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1541800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S46" s="3">
         <v>1767100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="3">
         <v>2025100</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3">
         <v>1698100</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="3">
         <v>1606800</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3">
         <v>1925500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>2228600</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>1522300</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>2408400</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI46" s="3">
         <v>3356600</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK46" s="3">
         <v>3739600</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM46" s="3">
         <v>2239500</v>
       </c>
-      <c r="AL46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO46" s="3">
         <v>2502600</v>
       </c>
-      <c r="AN46" s="3" t="s">
+      <c r="AP46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>898000</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>961600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>930100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3">
         <v>823100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>830400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>874300</v>
-      </c>
-      <c r="K47" s="3">
-        <v>824200</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M47" s="3">
         <v>824200</v>
@@ -4783,317 +4993,335 @@
         <v>5</v>
       </c>
       <c r="O47" s="3">
+        <v>824200</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3">
         <v>980200</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3">
         <v>940100</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3">
         <v>950800</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>720500</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3">
         <v>194500</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>184400</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>207800</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>301200</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>322900</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI47" s="3">
         <v>243800</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK47" s="3">
         <v>262500</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM47" s="3">
         <v>1475400</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO47" s="3">
         <v>2340600</v>
       </c>
-      <c r="AN47" s="3" t="s">
+      <c r="AP47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8302300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8344300</v>
+      </c>
+      <c r="F48" s="3">
         <v>8488900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8311200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7635100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>7215000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7400600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7383800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7469900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>7093900</v>
-      </c>
-      <c r="L48" s="3">
-        <v>7013100</v>
       </c>
       <c r="M48" s="3">
         <v>7093900</v>
       </c>
       <c r="N48" s="3">
+        <v>7013100</v>
+      </c>
+      <c r="O48" s="3">
+        <v>7093900</v>
+      </c>
+      <c r="P48" s="3">
         <v>7029600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>7106400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>6814800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>6794100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>6625200</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3">
         <v>6262700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>6868400</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>7330200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>6439600</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>7700700</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI48" s="3">
         <v>6250900</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" s="3">
         <v>6519900</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM48" s="3">
         <v>6592800</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO48" s="3">
         <v>7006500</v>
       </c>
-      <c r="AN48" s="3" t="s">
+      <c r="AP48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3459400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3521300</v>
+      </c>
+      <c r="F49" s="3">
         <v>3610400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3707600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3473800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3079000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3194000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2982000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3104900</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3109200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>3000600</v>
       </c>
       <c r="M49" s="3">
         <v>3109200</v>
       </c>
       <c r="N49" s="3">
+        <v>3000600</v>
+      </c>
+      <c r="O49" s="3">
+        <v>3109200</v>
+      </c>
+      <c r="P49" s="3">
         <v>3096500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3194300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S49" s="3">
         <v>3171800</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3">
         <v>3258800</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3">
         <v>3265000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3">
         <v>3229600</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>3177800</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>3496400</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>4511500</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>4657100</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI49" s="3">
         <v>3514700</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK49" s="3">
         <v>3748600</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM49" s="3">
         <v>3605000</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO49" s="3">
         <v>3814900</v>
       </c>
-      <c r="AN49" s="3" t="s">
+      <c r="AP49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5208,8 +5436,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5324,124 +5558,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1180700</v>
+      </c>
+      <c r="F52" s="3">
         <v>137400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>41100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1163000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>204000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>93200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1173800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>195600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>160500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1232000</v>
       </c>
       <c r="M52" s="3">
         <v>160500</v>
       </c>
       <c r="N52" s="3">
+        <v>1232000</v>
+      </c>
+      <c r="O52" s="3">
+        <v>160500</v>
+      </c>
+      <c r="P52" s="3">
         <v>1288600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>427500</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3">
         <v>511400</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3">
         <v>779500</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>779700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3">
         <v>755000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>981800</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1100900</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>1278700</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>1246800</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI52" s="3">
         <v>1330800</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK52" s="3">
         <v>1208400</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM52" s="3">
         <v>1337400</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO52" s="3">
         <v>1632800</v>
       </c>
-      <c r="AN52" s="3" t="s">
+      <c r="AP52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5556,124 +5802,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14397300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>14899100</v>
+      </c>
+      <c r="F54" s="3">
         <v>14906700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>14581300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>14693000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>12990000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>13723300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13813800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>13543700</v>
-      </c>
-      <c r="K54" s="3">
-        <v>12825300</v>
-      </c>
-      <c r="L54" s="3">
-        <v>12729700</v>
       </c>
       <c r="M54" s="3">
         <v>12825300</v>
       </c>
       <c r="N54" s="3">
+        <v>12729700</v>
+      </c>
+      <c r="O54" s="3">
+        <v>12825300</v>
+      </c>
+      <c r="P54" s="3">
         <v>12975900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13250200</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="3">
         <v>13205200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3">
         <v>13808200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3">
         <v>13088500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="3">
         <v>12048600</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>13137800</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>14363800</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>14053300</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>15383600</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI54" s="3">
         <v>14696700</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK54" s="3">
         <v>15456500</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM54" s="3">
         <v>15250100</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO54" s="3">
         <v>17297300</v>
       </c>
-      <c r="AN54" s="3" t="s">
+      <c r="AP54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5714,8 +5972,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5756,37 +6016,39 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1468100</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>818400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1416300</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3">
         <v>620100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1336100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>593600</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1221600</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M57" s="3">
         <v>1221600</v>
@@ -5795,665 +6057,701 @@
         <v>5</v>
       </c>
       <c r="O57" s="3">
+        <v>1221600</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1262700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3">
         <v>1245900</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>1274900</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>1225200</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1125100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>1245800</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>1466300</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>1384600</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>1605200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI57" s="3">
         <v>1686500</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK57" s="3">
         <v>1702100</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM57" s="3">
         <v>1883800</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO57" s="3">
         <v>2158600</v>
       </c>
-      <c r="AN57" s="3" t="s">
+      <c r="AP57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>478700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>166000</v>
+      </c>
+      <c r="F58" s="3">
         <v>643400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>209000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>170800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1104700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1342500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>171500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>733900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>539300</v>
-      </c>
-      <c r="L58" s="3">
-        <v>157700</v>
       </c>
       <c r="M58" s="3">
         <v>539300</v>
       </c>
       <c r="N58" s="3">
+        <v>157700</v>
+      </c>
+      <c r="O58" s="3">
+        <v>539300</v>
+      </c>
+      <c r="P58" s="3">
         <v>169500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>386600</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3">
         <v>1017400</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3">
         <v>882500</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>1280200</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3">
         <v>826800</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>1153100</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>1263100</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>143500</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>862300</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI58" s="3">
         <v>643400</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK58" s="3">
         <v>20200</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM58" s="3">
         <v>19100</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO58" s="3">
         <v>862800</v>
       </c>
-      <c r="AN58" s="3" t="s">
+      <c r="AP58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>287900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1995800</v>
+      </c>
+      <c r="F59" s="3">
         <v>298200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>233700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2284900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>222600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>223900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2079000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>244300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>203100</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1902000</v>
       </c>
       <c r="M59" s="3">
         <v>203100</v>
       </c>
       <c r="N59" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="O59" s="3">
+        <v>203100</v>
+      </c>
+      <c r="P59" s="3">
         <v>1533000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>213800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3">
         <v>212200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3">
         <v>250400</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3">
         <v>274000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3">
         <v>251300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>245500</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>345600</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>383500</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>411600</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI59" s="3">
         <v>88900</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK59" s="3">
         <v>396100</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM59" s="3">
         <v>66200</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO59" s="3">
         <v>63400</v>
       </c>
-      <c r="AN59" s="3" t="s">
+      <c r="AP59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2234700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2161900</v>
+      </c>
+      <c r="F60" s="3">
         <v>2490300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1859100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2455700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2627600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2902600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2250500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2257100</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1964000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>2059700</v>
       </c>
       <c r="M60" s="3">
         <v>1964000</v>
       </c>
       <c r="N60" s="3">
+        <v>2059700</v>
+      </c>
+      <c r="O60" s="3">
+        <v>1964000</v>
+      </c>
+      <c r="P60" s="3">
         <v>1702500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1863000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S60" s="3">
         <v>2475400</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="3">
         <v>2407800</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3">
         <v>2779400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="3">
         <v>2203300</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3">
         <v>2644400</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>3075000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>1911700</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>2879200</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI60" s="3">
         <v>2418900</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK60" s="3">
         <v>2118300</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM60" s="3">
         <v>1969100</v>
       </c>
-      <c r="AL60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO60" s="3">
         <v>3084800</v>
       </c>
-      <c r="AN60" s="3" t="s">
+      <c r="AP60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7822500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>8026100</v>
+      </c>
+      <c r="F61" s="3">
         <v>7716300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>8192600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7920400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6409600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6642000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7510000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7058700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>6897400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>6923200</v>
       </c>
       <c r="M61" s="3">
         <v>6897400</v>
       </c>
       <c r="N61" s="3">
+        <v>6923200</v>
+      </c>
+      <c r="O61" s="3">
+        <v>6897400</v>
+      </c>
+      <c r="P61" s="3">
         <v>6958900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>6580300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>6476600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>6626500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>6312500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7375100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>6355400</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>6590800</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>7029800</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>7596300</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>9050000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>9186400</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>7731000</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>8503600</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
         <v>8634800</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
         <v>9269600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>153100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>389700</v>
+      </c>
+      <c r="F62" s="3">
         <v>176100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>179700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>152400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>131500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>133900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>146700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>121600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>137600</v>
-      </c>
-      <c r="L62" s="3">
-        <v>143900</v>
       </c>
       <c r="M62" s="3">
         <v>137600</v>
       </c>
       <c r="N62" s="3">
+        <v>143900</v>
+      </c>
+      <c r="O62" s="3">
+        <v>137600</v>
+      </c>
+      <c r="P62" s="3">
         <v>192300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>762000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3">
         <v>643100</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3">
         <v>523600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3">
         <v>538500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3">
         <v>639300</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>758200</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>765800</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>1122300</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>1096500</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI62" s="3">
         <v>1021100</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK62" s="3">
         <v>926800</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM62" s="3">
         <v>700100</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO62" s="3">
         <v>716000</v>
       </c>
-      <c r="AN62" s="3" t="s">
+      <c r="AP62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6568,8 +6866,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6684,8 +6988,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6800,124 +7110,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10591800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10577700</v>
+      </c>
+      <c r="F66" s="3">
         <v>10725600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>10541400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>10528500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9331200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>9828600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9907200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9607600</v>
-      </c>
-      <c r="K66" s="3">
-        <v>9184500</v>
-      </c>
-      <c r="L66" s="3">
-        <v>9126800</v>
       </c>
       <c r="M66" s="3">
         <v>9184500</v>
       </c>
       <c r="N66" s="3">
+        <v>9126800</v>
+      </c>
+      <c r="O66" s="3">
+        <v>9184500</v>
+      </c>
+      <c r="P66" s="3">
         <v>8853800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>9207500</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3">
         <v>9747200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3">
         <v>10308700</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>9674400</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3">
         <v>9434400</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>10433500</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>11438300</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>12085200</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>13162100</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI66" s="3">
         <v>11171100</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK66" s="3">
         <v>11549800</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM66" s="3">
         <v>11304000</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO66" s="3">
         <v>13070400</v>
       </c>
-      <c r="AN66" s="3" t="s">
+      <c r="AP66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6958,8 +7280,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7074,8 +7398,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7190,8 +7520,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7306,8 +7642,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7422,37 +7764,43 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5514700</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>-5661600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-5826200</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3">
         <v>-5181700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-5514800</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>-5692500</v>
-      </c>
-      <c r="K72" s="3">
-        <v>-5842800</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M72" s="3">
         <v>-5842800</v>
@@ -7461,85 +7809,91 @@
         <v>5</v>
       </c>
       <c r="O72" s="3">
+        <v>-5842800</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-6049700</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3">
         <v>-6237000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>-6375600</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>-6223200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-6471100</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-7232700</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>-7707200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-8165400</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>-7968000</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI72" s="3">
         <v>-7127100</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK72" s="3">
         <v>-6978800</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM72" s="3">
         <v>-7174000</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO72" s="3">
         <v>-7406700</v>
       </c>
-      <c r="AN72" s="3" t="s">
+      <c r="AP72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7654,8 +8008,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7770,8 +8130,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7886,124 +8252,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3754100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4321500</v>
+      </c>
+      <c r="F76" s="3">
         <v>4129400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3987100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4164500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3655700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3891600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3906600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3932800</v>
-      </c>
-      <c r="K76" s="3">
-        <v>3638600</v>
-      </c>
-      <c r="L76" s="3">
-        <v>3602900</v>
       </c>
       <c r="M76" s="3">
         <v>3638600</v>
       </c>
       <c r="N76" s="3">
+        <v>3602900</v>
+      </c>
+      <c r="O76" s="3">
+        <v>3638600</v>
+      </c>
+      <c r="P76" s="3">
         <v>4122100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4042700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3684100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3458000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3665100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3499500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3370700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3414200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>2787800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2614200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>2509600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2704400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>3071200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>2925500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>2255200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>1968100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>2312300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>2221500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>2241800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>3525700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>3799100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>3906800</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM76" s="3">
         <v>3946000</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO76" s="3">
         <v>4226900</v>
       </c>
-      <c r="AN76" s="3" t="s">
+      <c r="AP76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8118,129 +8496,141 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45107</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45199</v>
       </c>
       <c r="M80" s="2">
         <v>45107</v>
       </c>
       <c r="N80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="O80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8277,86 +8667,92 @@
       <c r="N81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>211600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>228000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>202400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>193100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>170200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>199200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>846400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>143900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>174500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>137000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>148400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>135500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>98100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>384600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>270600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>106500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>104100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>249200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>107600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>111100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>111100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>269300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>108000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>207800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8397,55 +8793,57 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>207500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>72500</v>
+      </c>
+      <c r="F83" s="3">
         <v>321400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>193100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>80700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>312200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>205300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>60900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>337700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>238800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>228500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>337700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>238800</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -8474,47 +8872,53 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>896400</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>913200</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI83" s="3">
         <v>835600</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK83" s="3">
         <v>801100</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM83" s="3">
         <v>796600</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO83" s="3">
         <v>883900</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AP83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8629,8 +9033,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8745,8 +9155,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8861,8 +9277,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8977,8 +9399,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9093,55 +9521,61 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>660300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>463500</v>
+      </c>
+      <c r="F89" s="3">
         <v>819500</v>
       </c>
-      <c r="E89" s="3">
-        <v>596600</v>
-      </c>
-      <c r="F89" s="3">
-        <v>513400</v>
-      </c>
       <c r="G89" s="3">
+        <v>597800</v>
+      </c>
+      <c r="H89" s="3">
+        <v>512300</v>
+      </c>
+      <c r="I89" s="3">
         <v>735100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>612900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>550200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>753800</v>
-      </c>
-      <c r="K89" s="3">
-        <v>580800</v>
-      </c>
-      <c r="L89" s="3">
-        <v>552500</v>
       </c>
       <c r="M89" s="3">
         <v>580800</v>
       </c>
       <c r="N89" s="3">
+        <v>552500</v>
+      </c>
+      <c r="O89" s="3">
+        <v>580800</v>
+      </c>
+      <c r="P89" s="3">
         <v>551900</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S89" s="3">
         <v>0</v>
@@ -9170,47 +9604,53 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
+      <c r="AB89" s="3">
+        <v>0</v>
       </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>1014100</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>1348500</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI89" s="3">
         <v>1062900</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK89" s="3">
         <v>1249900</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM89" s="3">
         <v>938000</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO89" s="3">
         <v>1263000</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AP89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9251,55 +9691,57 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-265100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-245600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-340500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-277200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-250800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-260900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-282900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-277300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-317200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-245600</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-250800</v>
       </c>
       <c r="M91" s="3">
         <v>-245600</v>
       </c>
       <c r="N91" s="3">
+        <v>-250800</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-245600</v>
+      </c>
+      <c r="P91" s="3">
         <v>-262900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-257000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-336000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-336000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-254000</v>
       </c>
       <c r="S91" s="3">
         <v>-336000</v>
@@ -9308,67 +9750,73 @@
         <v>-254000</v>
       </c>
       <c r="U91" s="3">
+        <v>-336000</v>
+      </c>
+      <c r="V91" s="3">
+        <v>-254000</v>
+      </c>
+      <c r="W91" s="3">
         <v>-207400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-327700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-62800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-418300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-194200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-313900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-77000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-466700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-484700</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-514600</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-419400</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-482500</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-442100</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO91" s="3">
         <v>111500</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AP91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9483,8 +9931,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9599,55 +10053,61 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-84500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-494600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-508400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-129200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-516600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-435900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-570000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-345200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-458700</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-385400</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-437100</v>
       </c>
       <c r="M94" s="3">
         <v>-385400</v>
       </c>
       <c r="N94" s="3">
+        <v>-437100</v>
+      </c>
+      <c r="O94" s="3">
+        <v>-385400</v>
+      </c>
+      <c r="P94" s="3">
         <v>-267300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -9676,47 +10136,53 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-123500</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-89900</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-340400</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-812300</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM94" s="3">
         <v>127900</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-699600</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AP94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9757,50 +10223,52 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>475300</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3">
         <v>35200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>463900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>4300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>31100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>411400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>10800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>33200</v>
-      </c>
-      <c r="K96" s="3">
-        <v>417000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>217000</v>
       </c>
       <c r="M96" s="3">
         <v>417000</v>
       </c>
       <c r="N96" s="3">
+        <v>217000</v>
+      </c>
+      <c r="O96" s="3">
+        <v>417000</v>
+      </c>
+      <c r="P96" s="3">
         <v>10900</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -9838,43 +10306,49 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-395300</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-198700</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-396400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-173900</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-401700</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-165500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9989,8 +10463,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10105,8 +10585,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10221,55 +10707,61 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-762000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>81900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-194900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1553700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>628000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-77600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-288200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>291300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-74100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-414800</v>
-      </c>
-      <c r="L100" s="3">
-        <v>66700</v>
       </c>
       <c r="M100" s="3">
         <v>-414800</v>
       </c>
       <c r="N100" s="3">
+        <v>66700</v>
+      </c>
+      <c r="O100" s="3">
+        <v>-414800</v>
+      </c>
+      <c r="P100" s="3">
         <v>-242300</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S100" s="3">
         <v>0</v>
@@ -10298,47 +10790,53 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
+      <c r="AB100" s="3">
+        <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-1162300</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-1711700</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-411800</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-507100</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM100" s="3">
         <v>-1361000</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO100" s="3">
         <v>-363900</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AP100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10375,11 +10873,11 @@
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10438,70 +10936,76 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>5</v>
+      <c r="AJ101" s="3">
+        <v>0</v>
       </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM101" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM101" s="3">
-        <v>0</v>
-      </c>
       <c r="AN101" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-186200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>50700</v>
+      </c>
+      <c r="F102" s="3">
         <v>116200</v>
       </c>
-      <c r="E102" s="3">
-        <v>-1086300</v>
-      </c>
-      <c r="F102" s="3">
-        <v>624700</v>
-      </c>
       <c r="G102" s="3">
+        <v>-1085100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>623600</v>
+      </c>
+      <c r="I102" s="3">
         <v>221600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-245400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>496300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>221100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-219400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>182000</v>
       </c>
       <c r="M102" s="3">
         <v>-219400</v>
       </c>
       <c r="N102" s="3">
+        <v>182000</v>
+      </c>
+      <c r="O102" s="3">
+        <v>-219400</v>
+      </c>
+      <c r="P102" s="3">
         <v>42400</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S102" s="3">
         <v>0</v>
@@ -10530,43 +11034,49 @@
       <c r="AA102" s="3">
         <v>0</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
+      <c r="AB102" s="3">
+        <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-271700</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-516900</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI102" s="3">
         <v>216300</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK102" s="3">
         <v>-69600</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM102" s="3">
         <v>-296200</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO102" s="3">
         <v>261800</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AP102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
